--- a/Documentos/Documentos Excel - Hojas de calculo/Formato Condicional Avanzado.xlsx
+++ b/Documentos/Documentos Excel - Hojas de calculo/Formato Condicional Avanzado.xlsx
@@ -14,33 +14,27 @@
     <sheet name="Formato Condicional(Max y Min)" sheetId="4" r:id="rId5"/>
     <sheet name="Formato Condicional(Entre valor" sheetId="7" r:id="rId6"/>
     <sheet name="Formato Condicional(Borrar form" sheetId="8" r:id="rId7"/>
-    <sheet name="Formato condicional(Por fil (2" sheetId="10" r:id="rId8"/>
-    <sheet name="Formato condicional(Formula)" sheetId="11" r:id="rId9"/>
+    <sheet name="Formato condicional(Formula)" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="Cantidad" localSheetId="6">#REF!</definedName>
     <definedName name="Cantidad" localSheetId="5">#REF!</definedName>
-    <definedName name="Cantidad" localSheetId="8">#REF!</definedName>
     <definedName name="Cantidad" localSheetId="7">#REF!</definedName>
     <definedName name="Cantidad">#REF!</definedName>
     <definedName name="Mes" localSheetId="6">#REF!</definedName>
     <definedName name="Mes" localSheetId="5">#REF!</definedName>
-    <definedName name="Mes" localSheetId="8">#REF!</definedName>
     <definedName name="Mes" localSheetId="7">#REF!</definedName>
     <definedName name="Mes">#REF!</definedName>
     <definedName name="Sales" localSheetId="6">#REF!</definedName>
     <definedName name="Sales" localSheetId="5">#REF!</definedName>
-    <definedName name="Sales" localSheetId="8">#REF!</definedName>
     <definedName name="Sales" localSheetId="7">#REF!</definedName>
     <definedName name="Sales">#REF!</definedName>
     <definedName name="Tipo" localSheetId="6">#REF!</definedName>
     <definedName name="Tipo" localSheetId="5">#REF!</definedName>
-    <definedName name="Tipo" localSheetId="8">#REF!</definedName>
     <definedName name="Tipo" localSheetId="7">#REF!</definedName>
     <definedName name="Tipo">#REF!</definedName>
     <definedName name="Vendedor" localSheetId="6">#REF!</definedName>
     <definedName name="Vendedor" localSheetId="5">#REF!</definedName>
-    <definedName name="Vendedor" localSheetId="8">#REF!</definedName>
     <definedName name="Vendedor" localSheetId="7">#REF!</definedName>
     <definedName name="Vendedor">#REF!</definedName>
   </definedNames>
@@ -49,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="159">
   <si>
     <t>FECHA</t>
   </si>
@@ -773,42 +767,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <font>
         <b val="0"/>
@@ -885,74 +844,9 @@
     <dxf>
       <font>
         <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
+        <i/>
+        <strike/>
       </font>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1255,7 +1149,7 @@
         <xdr:cNvPr id="2" name="Flecha: pentágono 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00E00A52-60BD-4A78-95EA-24E240E87B25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00E00A52-60BD-4A78-95EA-24E240E87B25}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1344,7 +1238,7 @@
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FD07BD2-A1BE-42E7-BC98-60DD444BD85B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6FD07BD2-A1BE-42E7-BC98-60DD444BD85B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1388,7 +1282,7 @@
         <xdr:cNvPr id="4" name="Flecha: a la derecha 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D08D115-B3AA-4048-87A7-CD3C5595A09D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2D08D115-B3AA-4048-87A7-CD3C5595A09D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1451,7 +1345,7 @@
         <xdr:cNvPr id="5" name="Símbolo &quot;No permitido&quot; 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{103EAEB5-18CE-499F-AB0A-8CAD08114D73}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{103EAEB5-18CE-499F-AB0A-8CAD08114D73}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1521,7 +1415,7 @@
         <xdr:cNvPr id="6" name="Forma en L 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{751E690D-E023-422C-851C-BC8AB31FF326}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{751E690D-E023-422C-851C-BC8AB31FF326}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1587,7 +1481,7 @@
         <xdr:cNvPr id="7" name="Imagen 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E259D9E-47D5-4F06-A33E-87D40779458E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3E259D9E-47D5-4F06-A33E-87D40779458E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1632,7 +1526,7 @@
         <xdr:cNvPr id="8" name="Imagen 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94E7C085-2830-4E0E-A7F4-5B1564B257C1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{94E7C085-2830-4E0E-A7F4-5B1564B257C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1682,7 +1576,7 @@
         <xdr:cNvPr id="2" name="Flecha: pentágono 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32113FA1-C79A-4C8A-9894-E6126B45395D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{32113FA1-C79A-4C8A-9894-E6126B45395D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1784,7 +1678,7 @@
         <xdr:cNvPr id="2" name="Flecha: pentágono 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DE319C5-9A7B-4A59-91CD-9D8879791D5E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1DE319C5-9A7B-4A59-91CD-9D8879791D5E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1878,7 +1772,7 @@
         <xdr:cNvPr id="2" name="Flecha: pentágono 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{926D5F7F-D811-4DA8-9546-0154D9E52EA8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{926D5F7F-D811-4DA8-9546-0154D9E52EA8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1972,7 +1866,7 @@
         <xdr:cNvPr id="2" name="Flecha: pentágono 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{763BEAF1-90C9-4D38-9BEA-3CC32AB31C56}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{763BEAF1-90C9-4D38-9BEA-3CC32AB31C56}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2088,7 +1982,7 @@
         <xdr:cNvPr id="2" name="Flecha: pentágono 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8ED18B7E-B740-440C-995F-AB58B78E8340}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ED18B7E-B740-440C-995F-AB58B78E8340}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2201,7 +2095,7 @@
         <xdr:cNvPr id="2" name="Flecha: pentágono 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0C529325-9BD1-4CB9-B4C0-5721269A31A2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C529325-9BD1-4CB9-B4C0-5721269A31A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2295,434 +2189,7 @@
         <xdr:cNvPr id="2" name="Flecha: pentágono 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00E00A52-60BD-4A78-95EA-24E240E87B25}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="566738" y="166688"/>
-          <a:ext cx="5510212" cy="704850"/>
-        </a:xfrm>
-        <a:prstGeom prst="homePlate">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFF00"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent4">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent4"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent4"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="es-PE" sz="1800">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Century Schoolbook" panose="02040604050505020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="AngsanaUPC" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t>Formato condicional resaltar por fila cuando la existencia es cero</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="es-PE" sz="1800">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Century Schoolbook" panose="02040604050505020304" pitchFamily="18" charset="0"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="AngsanaUPC" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>114299</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>93055</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>367818</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>210241</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6FD07BD2-A1BE-42E7-BC98-60DD444BD85B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6076950" y="1283680"/>
-          <a:ext cx="0" cy="2736561"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>385763</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>152402</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>952501</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>71438</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Flecha: a la derecha 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2D08D115-B3AA-4048-87A7-CD3C5595A09D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6076950" y="2771777"/>
-          <a:ext cx="0" cy="633411"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightArrow">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100"/>
-            <a:t>Verdadero o falso</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>814388</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Símbolo &quot;No permitido&quot; 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{103EAEB5-18CE-499F-AB0A-8CAD08114D73}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6076950" y="4786312"/>
-          <a:ext cx="0" cy="395288"/>
-        </a:xfrm>
-        <a:prstGeom prst="noSmoking">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-GB" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>519114</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>80961</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>738189</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>176211</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Forma en L 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{751E690D-E023-422C-851C-BC8AB31FF326}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="19043596">
-          <a:off x="6076950" y="6348411"/>
-          <a:ext cx="0" cy="333375"/>
-        </a:xfrm>
-        <a:prstGeom prst="corner">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent6"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-GB" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4762</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>214312</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>82750</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Imagen 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3E259D9E-47D5-4F06-A33E-87D40779458E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:srcRect t="22090"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6076950" y="4605337"/>
-          <a:ext cx="0" cy="344688"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>104916</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>85805</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Imagen 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{94E7C085-2830-4E0E-A7F4-5B1564B257C1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:srcRect t="23330"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6076950" y="6134100"/>
-          <a:ext cx="0" cy="457280"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>566738</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>166688</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>157163</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Flecha: pentágono 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7D511C77-DE9B-47A3-8C97-938D1EB03887}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D511C77-DE9B-47A3-8C97-938D1EB03887}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2830,7 +2297,7 @@
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DA4D888B-8140-446D-9236-F995AF441FAB}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA4D888B-8140-446D-9236-F995AF441FAB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3027,12 +2494,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabla6" displayName="Tabla6" ref="C7:E24" totalsRowShown="0" headerRowDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabla6" displayName="Tabla6" ref="C7:E24" totalsRowShown="0" headerRowDxfId="18">
   <autoFilter ref="C7:E24"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="NOMBRE" dataDxfId="25"/>
-    <tableColumn id="2" name="UNIDAD" dataDxfId="24"/>
-    <tableColumn id="3" name="EXISTENCIA" dataDxfId="23"/>
+    <tableColumn id="1" name="NOMBRE" dataDxfId="17"/>
+    <tableColumn id="2" name="UNIDAD" dataDxfId="16"/>
+    <tableColumn id="3" name="EXISTENCIA" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3042,11 +2509,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla13" displayName="Tabla13" ref="B8:F45">
   <autoFilter ref="B8:F45"/>
   <tableColumns count="5">
-    <tableColumn id="2" name="FECHA" totalsRowDxfId="22"/>
-    <tableColumn id="6" name="# FACTURA" totalsRowDxfId="21"/>
-    <tableColumn id="4" name="DESCRIPCIÓN" totalsRowFunction="count" totalsRowDxfId="20"/>
-    <tableColumn id="5" name="PROVEEDOR" totalsRowDxfId="19"/>
-    <tableColumn id="11" name="MONTO ($)" totalsRowFunction="sum" totalsRowDxfId="18"/>
+    <tableColumn id="2" name="FECHA" totalsRowDxfId="14"/>
+    <tableColumn id="6" name="# FACTURA" totalsRowDxfId="13"/>
+    <tableColumn id="4" name="DESCRIPCIÓN" totalsRowFunction="count" totalsRowDxfId="12"/>
+    <tableColumn id="5" name="PROVEEDOR" totalsRowDxfId="11"/>
+    <tableColumn id="11" name="MONTO ($)" totalsRowFunction="sum" totalsRowDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3056,35 +2523,23 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla134" displayName="Tabla134" ref="B10:F47">
   <autoFilter ref="B10:F47"/>
   <tableColumns count="5">
-    <tableColumn id="2" name="FECHA" totalsRowDxfId="17"/>
-    <tableColumn id="6" name="# FACTURA" totalsRowDxfId="16"/>
-    <tableColumn id="4" name="DESCRIPCIÓN" totalsRowFunction="count" totalsRowDxfId="15"/>
-    <tableColumn id="5" name="PROVEEDOR" totalsRowDxfId="14"/>
-    <tableColumn id="11" name="MONTO ($)" totalsRowFunction="sum" totalsRowDxfId="13"/>
+    <tableColumn id="2" name="FECHA" totalsRowDxfId="9"/>
+    <tableColumn id="6" name="# FACTURA" totalsRowDxfId="8"/>
+    <tableColumn id="4" name="DESCRIPCIÓN" totalsRowFunction="count" totalsRowDxfId="7"/>
+    <tableColumn id="5" name="PROVEEDOR" totalsRowDxfId="6"/>
+    <tableColumn id="11" name="MONTO ($)" totalsRowFunction="sum" totalsRowDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabla66" displayName="Tabla66" ref="C7:E24" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="C7:E24"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="NOMBRE" dataDxfId="11"/>
-    <tableColumn id="2" name="UNIDAD" dataDxfId="10"/>
-    <tableColumn id="3" name="EXISTENCIA" dataDxfId="9"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabla68" displayName="Tabla68" ref="C7:E29" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabla68" displayName="Tabla68" ref="C7:E29" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="C7:E29"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Producto" dataDxfId="7"/>
-    <tableColumn id="2" name="Descripción" dataDxfId="6"/>
-    <tableColumn id="3" name="Código EAN" dataDxfId="5"/>
+    <tableColumn id="1" name="Producto" dataDxfId="2"/>
+    <tableColumn id="2" name="Descripción" dataDxfId="1"/>
+    <tableColumn id="3" name="Código EAN" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -42069,7 +41524,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C9:G24">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -42091,236 +41546,6 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C7:O28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="18.75" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="10.7109375" style="1"/>
-    <col min="3" max="3" width="35" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="1"/>
-    <col min="7" max="14" width="13.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="10.7109375" style="1" collapsed="1"/>
-    <col min="16" max="16384" width="10.7109375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="7" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C7" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C8" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="19">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C9" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" s="19">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C10" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C11" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="19">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C12" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="19">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C13" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C14" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" s="19">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C15" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="19">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C16" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" s="19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="C18" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" s="19">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="19">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" s="19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" s="19">
-        <v>20</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="C23" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="19">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="C24" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="19">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="I28" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C7:E29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
